--- a/Cell survival results/2026_3_18/Multiplicity proton 18-3.xlsx
+++ b/Cell survival results/2026_3_18/Multiplicity proton 18-3.xlsx
@@ -1,11 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29912"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29822"/>
   <workbookPr defaultThemeVersion="166925"/>
-  <xr:revisionPtr revIDLastSave="37" documentId="11_E60897F41BE170836B02CE998F75CCDC64E183C8" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{3070436A-49F4-49AB-8815-46BABFEDFDF1}"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\bhaan\Documents\#Master Degree\Thesis\Thesis_project\Cell survival results\2026_3_18\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D62EAEB8-78F1-4FA5-AC1B-517310E760EF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="105" windowWidth="14805" windowHeight="8010" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -64,7 +69,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -76,7 +81,7 @@
       <b/>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="Aptos Narrow"/>
+      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
@@ -122,9 +127,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 Theme">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2013 - 2022">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -162,7 +167,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2013 - 2022">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -268,7 +273,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2013 - 2022">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -410,7 +415,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -419,9 +424,9 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:E9"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:5">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -438,7 +443,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:5">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
         <v>2</v>
       </c>
@@ -452,11 +457,11 @@
         <v>1</v>
       </c>
       <c r="E2">
-        <f>SUM(B2:D2)</f>
+        <f t="shared" ref="E2:E8" si="0">SUM(B2:D2)</f>
         <v>45</v>
       </c>
     </row>
-    <row r="3" spans="1:5">
+    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A3" s="1" t="s">
         <v>3</v>
       </c>
@@ -470,11 +475,11 @@
         <v>0</v>
       </c>
       <c r="E3">
-        <f>SUM(B3:D3)</f>
+        <f t="shared" si="0"/>
         <v>76</v>
       </c>
     </row>
-    <row r="4" spans="1:5">
+    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A4" s="1" t="s">
         <v>4</v>
       </c>
@@ -488,11 +493,11 @@
         <v>0</v>
       </c>
       <c r="E4">
-        <f>SUM(B4:D4)</f>
+        <f t="shared" si="0"/>
         <v>21</v>
       </c>
     </row>
-    <row r="5" spans="1:5">
+    <row r="5" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A5" s="1" t="s">
         <v>5</v>
       </c>
@@ -506,11 +511,11 @@
         <v>0</v>
       </c>
       <c r="E5">
-        <f>SUM(B5:D5)</f>
+        <f t="shared" si="0"/>
         <v>26</v>
       </c>
     </row>
-    <row r="6" spans="1:5">
+    <row r="6" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A6" s="1" t="s">
         <v>6</v>
       </c>
@@ -524,11 +529,11 @@
         <v>0</v>
       </c>
       <c r="E6">
-        <f>SUM(B6:D6)</f>
+        <f t="shared" si="0"/>
         <v>39</v>
       </c>
     </row>
-    <row r="7" spans="1:5">
+    <row r="7" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A7" s="1" t="s">
         <v>7</v>
       </c>
@@ -542,11 +547,11 @@
         <v>0</v>
       </c>
       <c r="E7">
-        <f>SUM(B7:D7)</f>
+        <f t="shared" si="0"/>
         <v>58</v>
       </c>
     </row>
-    <row r="8" spans="1:5">
+    <row r="8" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A8" s="1" t="s">
         <v>8</v>
       </c>
@@ -560,11 +565,11 @@
         <v>0</v>
       </c>
       <c r="E8">
-        <f>SUM(B8:D8)</f>
+        <f t="shared" si="0"/>
         <v>47</v>
       </c>
     </row>
-    <row r="9" spans="1:5">
+    <row r="9" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A9" s="1" t="s">
         <v>1</v>
       </c>
